--- a/results/Int All Data 0.6/Rando_9_permute.xlsx
+++ b/results/Int All Data 0.6/Rando_9_permute.xlsx
@@ -440,1547 +440,1547 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8284884747078964</v>
+        <v>0.8335848423876593</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8328259027851319</v>
+        <v>0.8357778248437997</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8394710367467966</v>
+        <v>0.8374104274771436</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8394710367467966</v>
+        <v>0.8402476261075223</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8344408556602774</v>
+        <v>0.8428200783649265</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.836139644886865</v>
+        <v>0.8415669455328463</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.829476861167002</v>
+        <v>0.8418802287408662</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8306152705707932</v>
+        <v>0.8409403791168061</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8336333792227046</v>
+        <v>0.8415669455328463</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8374104274771436</v>
+        <v>0.8431333615729464</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8374104274771436</v>
+        <v>0.8428200783649265</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8386635603092238</v>
+        <v>0.8418802287408662</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8383326273430054</v>
+        <v>0.8418802287408662</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.8383326273430054</v>
+        <v>0.838054643651382</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8383326273430054</v>
+        <v>0.838054643651382</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8383326273430054</v>
+        <v>0.8377413604433619</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8383326273430054</v>
+        <v>0.8371147940273218</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8386459105510254</v>
+        <v>0.743765222916446</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8436584418793462</v>
+        <v>0.743765222916446</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8477487733418052</v>
+        <v>0.7438975961029334</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.8474354901337852</v>
+        <v>0.722060432772071</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.8432966218362808</v>
+        <v>0.7058844293833174</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.8432304352430372</v>
+        <v>0.7194570934378199</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.8419773024109569</v>
+        <v>0.7194570934378199</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.8419773024109569</v>
+        <v>0.7254094743902009</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.8451763210844012</v>
+        <v>0.7344638003459352</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8483753397578453</v>
+        <v>0.7412589572522856</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.8445497546683611</v>
+        <v>0.7406323908362455</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.8441702848670973</v>
+        <v>0.7447889088919482</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.8429171520350172</v>
+        <v>0.7487954040029652</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.842603868826997</v>
+        <v>0.7500485368350454</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8412183628084295</v>
+        <v>0.7453978255497899</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.8427847788485298</v>
+        <v>0.7510369232941508</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8467427371245014</v>
+        <v>0.7510369232941508</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8438570016590773</v>
+        <v>0.7510369232941508</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.826736736206714</v>
+        <v>0.7510369232941508</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8323758339510748</v>
+        <v>0.7507236400861308</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8024727311235835</v>
+        <v>0.7530489957287585</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8024727311235835</v>
+        <v>0.7529342723004695</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.7997679056796922</v>
+        <v>0.7519944226764094</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.800460658688976</v>
+        <v>0.7506265664160401</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8025389177168273</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.7982676762328356</v>
+        <v>0.7591513996258251</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.7969483568075117</v>
+        <v>0.7581453634085213</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8034302305058421</v>
+        <v>0.7564465741819337</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.7997193688446469</v>
+        <v>0.7564465741819337</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8034302305058421</v>
+        <v>0.7545668749338135</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8044362667231459</v>
+        <v>0.7567598573899538</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8077676585830774</v>
+        <v>0.7545668749338135</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.8088398813936248</v>
+        <v>0.7536270253097532</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8088398813936248</v>
+        <v>0.7511207596455929</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8212917858025345</v>
+        <v>0.7513678562603692</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.8212917858025345</v>
+        <v>0.7510545730523492</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.8212917858025345</v>
+        <v>0.7508074764375728</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.8265867132620284</v>
+        <v>0.7084215821243249</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.8262072434607646</v>
+        <v>0.7083553955310813</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.8253159306717498</v>
+        <v>0.7057829432736771</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.8182074905573793</v>
+        <v>0.7057829432736771</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.8202195629919871</v>
+        <v>0.7075126195771118</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.8200871898054997</v>
+        <v>0.7029457446432984</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.8216536058455999</v>
+        <v>0.7029457446432984</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.8223463588548837</v>
+        <v>0.6969271770976737</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.8223463588548837</v>
+        <v>0.6865535317166155</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.8130449362843729</v>
+        <v>0.6900658335980797</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7132973278266088</v>
+        <v>0.6900658335980797</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7126707614105687</v>
+        <v>0.6846252956334499</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6905776765858308</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.7083333333333334</v>
+        <v>0.6836854460093896</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.7057608810759293</v>
+        <v>0.6827455963853295</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.7057608810759293</v>
+        <v>0.6937105086660312</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.7088275265628861</v>
+        <v>0.6937105086660312</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.7081347735536023</v>
+        <v>0.692144092625931</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.7017190864485157</v>
+        <v>0.6928368456352149</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6950077658936072</v>
+        <v>0.6873963076705849</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6809232588513537</v>
+        <v>0.688022874086625</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.691380740583854</v>
+        <v>0.6887156270959087</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6921882170214269</v>
+        <v>0.6878243143068941</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6879831621306788</v>
+        <v>0.6878243143068941</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6942179392142328</v>
+        <v>0.6922941155706167</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6910851071340323</v>
+        <v>0.6920470189558403</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.6913983903420523</v>
+        <v>0.6955107840022592</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6261384094037912</v>
+        <v>0.6980832362596632</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6553134597056021</v>
+        <v>0.6737618694623884</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.6131261251720852</v>
+        <v>0.6826308729570405</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.6099932930918845</v>
+        <v>0.6845105722051608</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.6193123654205938</v>
+        <v>0.6806673373574782</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.6193123654205938</v>
+        <v>0.6811791803452293</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.596632426135762</v>
+        <v>0.6814924635532493</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.6222466377210631</v>
+        <v>0.6837516326026334</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.6196565357054609</v>
+        <v>0.6812453669384729</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5931863108475414</v>
+        <v>0.6802040312047725</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.584727664231</v>
+        <v>0.6795112781954887</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.6138541776977655</v>
+        <v>0.6810776942355889</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.6110831656606305</v>
+        <v>0.685481308906068</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.6110831656606305</v>
+        <v>0.6892098203254615</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5906668078647322</v>
+        <v>0.6963006106816336</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5595105722051608</v>
+        <v>0.692227928977373</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.588420876133997</v>
+        <v>0.6909086095520491</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.588420876133997</v>
+        <v>0.685993151893819</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.588420876133997</v>
+        <v>0.6896510642804193</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.6549384023438879</v>
+        <v>0.6822293409580289</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.6033658088884182</v>
+        <v>0.6822955275512725</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5774383140950969</v>
+        <v>0.6272900561262311</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5444200289456035</v>
+        <v>0.6279166225422712</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5441067457375833</v>
+        <v>0.6228202548625084</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5446671255603798</v>
+        <v>0.6221936884464683</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5459687952275054</v>
+        <v>0.6205610858131243</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5636317907444668</v>
+        <v>0.6111934766493698</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5633185075364467</v>
+        <v>0.6111934766493698</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5633185075364467</v>
+        <v>0.6152176215185852</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5633185075364467</v>
+        <v>0.5781751914998765</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5789385435419535</v>
+        <v>0.5823978961488228</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5430345229270359</v>
+        <v>0.6079944579759258</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5511798863355573</v>
+        <v>0.607928271382682</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5450951321966889</v>
+        <v>0.6066751385506018</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5392751244307953</v>
+        <v>0.6073678915598857</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5385823714215114</v>
+        <v>0.5927053549366373</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5370159553814113</v>
+        <v>0.5923920717286173</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5000882487909916</v>
+        <v>0.5637774012496028</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.4802808076529351</v>
+        <v>0.6117229693953192</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.4809073740689752</v>
+        <v>0.6219157047548448</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.4805279042677116</v>
+        <v>0.6143969077623637</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.4565727699530516</v>
+        <v>0.6006742207631756</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.4568022168096297</v>
+        <v>0.5528786755621448</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.4551034275830421</v>
+        <v>0.5149625825126196</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.4574773200607152</v>
+        <v>0.5001853224610823</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.4580200501253133</v>
+        <v>0.5001853224610823</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.4558270676691729</v>
+        <v>0.4976437572805252</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.4567669172932331</v>
+        <v>0.4976437572805252</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.4558270676691729</v>
+        <v>0.4949389318366338</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.4537002718062763</v>
+        <v>0.495565498252674</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>0.4518205725581559</v>
+        <v>0.4951860284514102</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>0.4543268382223163</v>
+        <v>0.4951860284514102</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.421202654523633</v>
+        <v>0.4997043665501782</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.423263263793286</v>
+        <v>0.4997043665501782</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>0.4297760245684634</v>
+        <v>0.4997043665501782</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.4297760245684634</v>
+        <v>0.504884570581383</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>0.4400481838398814</v>
+        <v>0.504716897878499</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>0.398169720074835</v>
+        <v>0.5064156871050867</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>0.4000494193229552</v>
+        <v>0.5144639768435173</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>0.3952045606975185</v>
+        <v>0.5139035970207209</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>0.382395248685093</v>
+        <v>0.5122048077941332</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>0.3879549225175615</v>
+        <v>0.5316327791309259</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>0.3873283561015214</v>
+        <v>0.5422711708849589</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>0.3657382893854354</v>
+        <v>0.5405723816583713</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>0.3657382893854354</v>
+        <v>0.5598194429736313</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>0.4089493098944544</v>
+        <v>0.5578073705390236</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>0.4427794839210702</v>
+        <v>0.4987468671679198</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>0.4427794839210702</v>
+        <v>0.5047830844717427</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>0.4481714850506548</v>
+        <v>0.5047830844717427</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>0.4754138868297504</v>
+        <v>0.5030357584101098</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>0.4754138868297504</v>
+        <v>0.5030357584101098</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>0.4690643863179075</v>
+        <v>0.4997043665501782</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>0.4488377634226411</v>
+        <v>0.4997043665501782</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>0.4904691305729111</v>
+        <v>0.4972642874792615</v>
       </c>
     </row>
   </sheetData>
